--- a/data/trans_camb/IP04D$individual-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 17,1</t>
+          <t>-8,33; 16,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,51; -0,7</t>
+          <t>-23,16; -2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,65; -0,41</t>
+          <t>-24,01; -0,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,47; -9,37</t>
+          <t>-31,34; -8,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 4,52</t>
+          <t>-12,84; 4,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,65; -7,73</t>
+          <t>-24,32; -7,68</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 56,7</t>
+          <t>-19,27; 57,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,62; -2,93</t>
+          <t>-55,12; -7,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,53; -0,34</t>
+          <t>-43,72; -0,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,52; -20,48</t>
+          <t>-58,54; -19,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 11,95</t>
+          <t>-27,31; 10,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,24; -20,46</t>
+          <t>-52,05; -20,76</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 8,65</t>
+          <t>-14,33; 8,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,03; -6,05</t>
+          <t>-27,44; -5,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 8,31</t>
+          <t>-13,64; 9,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,54; -8,36</t>
+          <t>-31,5; -7,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 5,33</t>
+          <t>-10,9; 5,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -10,28</t>
+          <t>-25,5; -9,68</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 26,93</t>
+          <t>-31,74; 25,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -17,12</t>
+          <t>-61,3; -16,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,66; 22,03</t>
+          <t>-27,7; 27,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,84; -21,06</t>
+          <t>-62,26; -18,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 15,24</t>
+          <t>-23,83; 14,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,69; -26,65</t>
+          <t>-56,5; -25,59</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 17,49</t>
+          <t>-7,56; 16,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -7,0</t>
+          <t>-29,12; -6,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 19,5</t>
+          <t>-2,81; 20,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,59; -5,71</t>
+          <t>-25,82; -5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 15,4</t>
+          <t>-1,21; 15,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,82; -9,22</t>
+          <t>-24,65; -9,15</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 72,24</t>
+          <t>-22,2; 65,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,8; -21,71</t>
+          <t>-82,42; -16,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 82,61</t>
+          <t>-8,47; 94,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,88; -21,57</t>
+          <t>-78,28; -22,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 61,03</t>
+          <t>-4,38; 63,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,22; -32,75</t>
+          <t>-75,18; -32,04</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 12,03</t>
+          <t>-2,99; 11,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,4; -5,98</t>
+          <t>-20,41; -5,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 3,88</t>
+          <t>-9,88; 3,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -0,45</t>
+          <t>-15,7; 0,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 5,88</t>
+          <t>-3,92; 6,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -5,0</t>
+          <t>-15,59; -4,23</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 53,18</t>
+          <t>-9,24; 53,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,73; -26,75</t>
+          <t>-67,95; -22,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 15,46</t>
+          <t>-30,4; 14,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,41; -1,8</t>
+          <t>-49,1; 1,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 23,23</t>
+          <t>-13,01; 25,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,3; -19,73</t>
+          <t>-52,7; -16,76</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 4,56</t>
+          <t>-11,13; 5,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,24; -3,39</t>
+          <t>-17,64; -2,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,88; -0,85</t>
+          <t>-18,46; -1,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 10,18</t>
+          <t>-19,53; 7,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -1,18</t>
+          <t>-12,14; -1,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 1,91</t>
+          <t>-16,57; 1,07</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 25,0</t>
+          <t>-41,98; 27,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,2; -14,54</t>
+          <t>-67,98; -13,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,48; -3,14</t>
+          <t>-56,26; -6,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 52,34</t>
+          <t>-63,89; 40,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -3,44</t>
+          <t>-43,08; -4,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,23; 10,49</t>
+          <t>-60,49; 6,96</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 18,86</t>
+          <t>-5,51; 21,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 8,22</t>
+          <t>-16,67; 7,79</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 8,55</t>
+          <t>-14,05; 9,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 2,84</t>
+          <t>-20,47; 1,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 10,38</t>
+          <t>-7,0; 10,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 1,45</t>
+          <t>-15,88; 1,18</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 127,63</t>
+          <t>-23,91; 138,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-60,51; 56,67</t>
+          <t>-61,64; 57,41</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 51,32</t>
+          <t>-48,55; 54,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 19,55</t>
+          <t>-70,53; 14,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 56,5</t>
+          <t>-26,15; 61,75</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 9,15</t>
+          <t>-60,66; 7,68</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,64</t>
+          <t>-1,44; 6,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -8,32</t>
+          <t>-16,3; -8,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,17; -0,16</t>
+          <t>-7,34; 0,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -6,63</t>
+          <t>-16,47; -7,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,27</t>
+          <t>-3,68; 2,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,27; -9,23</t>
+          <t>-15,36; -8,69</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 25,54</t>
+          <t>-4,73; 24,62</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-54,92; -30,98</t>
+          <t>-54,05; -31,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -0,57</t>
+          <t>-21,48; 1,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,41; -19,89</t>
+          <t>-47,55; -21,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 7,83</t>
+          <t>-11,56; 6,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,81; -30,24</t>
+          <t>-47,75; -29,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 16,86</t>
+          <t>-7,96; 16,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,16; -2,63</t>
+          <t>-22,43; -1,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,01; -0,17</t>
+          <t>-25,15; -0,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,34; -8,27</t>
+          <t>-33,16; -9,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 4,06</t>
+          <t>-12,44; 4,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,32; -7,68</t>
+          <t>-23,89; -8,03</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 57,05</t>
+          <t>-18,17; 54,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,12; -7,03</t>
+          <t>-54,28; -3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,72; -0,68</t>
+          <t>-45,07; -1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,54; -19,62</t>
+          <t>-61,66; -23,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 10,63</t>
+          <t>-26,86; 12,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -20,76</t>
+          <t>-52,08; -21,24</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 8,51</t>
+          <t>-14,39; 9,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,44; -5,54</t>
+          <t>-27,55; -6,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 9,78</t>
+          <t>-14,05; 8,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,5; -7,67</t>
+          <t>-29,96; -5,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 5,27</t>
+          <t>-10,28; 5,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,5; -9,68</t>
+          <t>-25,88; -10,2</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 25,47</t>
+          <t>-31,71; 27,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,3; -16,1</t>
+          <t>-62,85; -17,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; 27,91</t>
+          <t>-27,14; 21,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,26; -18,11</t>
+          <t>-61,23; -12,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 14,12</t>
+          <t>-22,44; 16,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; -25,59</t>
+          <t>-57,83; -26,84</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 16,02</t>
+          <t>-6,64; 16,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,12; -6,94</t>
+          <t>-27,73; -5,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 20,78</t>
+          <t>-4,59; 20,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,82; -5,45</t>
+          <t>-26,09; -5,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 15,51</t>
+          <t>-2,33; 15,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,65; -9,15</t>
+          <t>-24,99; -9,41</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 65,81</t>
+          <t>-19,78; 68,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,42; -16,92</t>
+          <t>-83,04; -17,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 94,76</t>
+          <t>-13,9; 89,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,28; -22,45</t>
+          <t>-79,2; -19,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 63,95</t>
+          <t>-6,92; 64,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-75,18; -32,04</t>
+          <t>-77,37; -37,1</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 11,77</t>
+          <t>-1,91; 12,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,41; -5,32</t>
+          <t>-20,42; -5,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 3,78</t>
+          <t>-9,67; 4,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 0,03</t>
+          <t>-15,95; 0,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,43</t>
+          <t>-4,31; 6,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -4,23</t>
+          <t>-15,88; -4,9</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 53,25</t>
+          <t>-6,5; 57,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,95; -22,18</t>
+          <t>-69,21; -25,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 14,61</t>
+          <t>-29,69; 16,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 1,54</t>
+          <t>-48,38; 2,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 25,27</t>
+          <t>-14,15; 23,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,7; -16,76</t>
+          <t>-52,48; -18,22</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 5,03</t>
+          <t>-11,57; 4,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -2,74</t>
+          <t>-19,06; -3,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,46; -1,75</t>
+          <t>-18,44; -1,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 7,24</t>
+          <t>-20,4; 6,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -1,23</t>
+          <t>-12,11; -1,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 1,07</t>
+          <t>-16,18; 2,12</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 27,43</t>
+          <t>-43,64; 25,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,98; -13,68</t>
+          <t>-70,0; -18,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,26; -6,86</t>
+          <t>-54,97; -5,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-63,89; 40,41</t>
+          <t>-65,09; 27,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,08; -4,57</t>
+          <t>-43,12; -5,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 6,96</t>
+          <t>-59,48; 11,25</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 21,23</t>
+          <t>-5,94; 20,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 7,79</t>
+          <t>-17,0; 7,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 9,29</t>
+          <t>-13,38; 8,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 1,78</t>
+          <t>-19,32; 2,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 10,98</t>
+          <t>-7,23; 10,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 1,18</t>
+          <t>-16,12; 1,13</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 138,65</t>
+          <t>-24,05; 141,58</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 57,41</t>
+          <t>-63,07; 48,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 54,74</t>
+          <t>-49,25; 49,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 14,03</t>
+          <t>-70,8; 12,66</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 61,75</t>
+          <t>-28,04; 60,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-60,66; 7,68</t>
+          <t>-60,39; 6,53</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,34</t>
+          <t>-1,43; 6,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -8,23</t>
+          <t>-16,37; -8,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,39</t>
+          <t>-7,37; 0,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,47; -7,04</t>
+          <t>-16,51; -7,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,0</t>
+          <t>-3,63; 2,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -8,69</t>
+          <t>-15,04; -8,75</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 24,62</t>
+          <t>-4,78; 23,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-54,05; -31,46</t>
+          <t>-53,62; -32,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 1,61</t>
+          <t>-21,49; 2,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -21,07</t>
+          <t>-47,97; -23,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 6,7</t>
+          <t>-11,26; 7,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,75; -29,55</t>
+          <t>-47,65; -29,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Clase-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-12,43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-19,26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>4,64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-12,41</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-12,43</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-20,64</t>
+          <t>-11,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,22</t>
+          <t>-15,37</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 16,39</t>
+          <t>-23,65; -0,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,43; -1,0</t>
+          <t>-29,94; -7,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -0,79</t>
+          <t>-6,46; 17,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,16; -9,9</t>
+          <t>-23,02; -0,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 4,84</t>
+          <t>-12,92; 4,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,89; -8,03</t>
+          <t>-23,33; -6,3</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-25,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-39,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>13,01%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-34,78%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-25,56%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-42,46%</t>
+          <t>-33,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-38,49%</t>
+          <t>-36,46%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 54,32</t>
+          <t>-43,53; -0,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -3,42</t>
+          <t>-54,62; -16,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,07; -1,47</t>
+          <t>-16,61; 56,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,66; -23,69</t>
+          <t>-55,65; -1,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 12,68</t>
+          <t>-27,62; 11,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,08; -21,24</t>
+          <t>-50,5; -17,64</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-20,09</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-16,62</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,49</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-19,53</t>
+          <t>-17,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-18,12</t>
+          <t>-18,93</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 9,01</t>
+          <t>-13,67; 8,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,55; -6,37</t>
+          <t>-31,28; -8,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 8,2</t>
+          <t>-13,08; 8,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,96; -5,96</t>
+          <t>-28,29; -6,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 5,88</t>
+          <t>-10,75; 5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,88; -10,2</t>
+          <t>-26,6; -11,17</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-5,69%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-45,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-6,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-42,84%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,69%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-44,65%</t>
+          <t>-45,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,87%</t>
+          <t>-45,81%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 27,68</t>
+          <t>-27,66; 22,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,85; -17,93</t>
+          <t>-63,99; -22,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 21,38</t>
+          <t>-29,67; 26,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,23; -12,83</t>
+          <t>-63,3; -19,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 16,05</t>
+          <t>-23,51; 15,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,83; -26,84</t>
+          <t>-59,46; -28,95</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-16,26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>4,64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-18,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,53</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-16,59</t>
+          <t>-18,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,43</t>
+          <t>-17,46</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 16,73</t>
+          <t>-5,55; 19,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -5,34</t>
+          <t>-26,15; -5,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 20,69</t>
+          <t>-7,88; 17,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,09; -5,06</t>
+          <t>-28,48; -7,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 15,55</t>
+          <t>-1,52; 15,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,99; -9,41</t>
+          <t>-24,68; -9,15</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-56,51%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>15,68%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-62,08%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-57,64%</t>
+          <t>-63,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-59,71%</t>
+          <t>-59,82%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 68,66</t>
+          <t>-16,69; 82,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,04; -17,68</t>
+          <t>-78,55; -19,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 89,53</t>
+          <t>-23,0; 72,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,2; -19,01</t>
+          <t>-84,4; -24,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 64,46</t>
+          <t>-4,76; 61,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,37; -37,1</t>
+          <t>-75,08; -33,12</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-8,12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>5,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-12,6</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-8,05</t>
+          <t>-10,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,39</t>
+          <t>-9,06</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 12,94</t>
+          <t>-10,74; 3,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -5,83</t>
+          <t>-16,03; -0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 4,15</t>
+          <t>-1,77; 12,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 0,47</t>
+          <t>-16,55; -3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,0</t>
+          <t>-3,93; 5,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,88; -4,9</t>
+          <t>-14,42; -4,03</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-10,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-27,96%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>19,98%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-47,9%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,9%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-27,71%</t>
+          <t>-38,61%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-37,44%</t>
+          <t>-32,66%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 57,6</t>
+          <t>-32,69; 15,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,21; -25,64</t>
+          <t>-50,71; 0,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 16,72</t>
+          <t>-5,98; 53,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 2,39</t>
+          <t>-56,48; -13,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 23,68</t>
+          <t>-12,92; 23,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,48; -18,22</t>
+          <t>-47,71; -13,88</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-9,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-10,98</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-3,64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-10,98</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,72</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,56</t>
+          <t>-11,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,22</t>
+          <t>-10,59</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 4,74</t>
+          <t>-17,88; -0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -3,73</t>
+          <t>-19,91; 8,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -1,63</t>
+          <t>-11,36; 4,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 6,2</t>
+          <t>-19,06; -3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -1,23</t>
+          <t>-12,49; -1,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 2,12</t>
+          <t>-16,6; -0,28</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-34,14%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-38,57%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-16,07%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-48,55%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-34,14%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-37,07%</t>
+          <t>-48,61%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,1%</t>
+          <t>-41,58%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 25,79</t>
+          <t>-54,48; -3,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,0; -18,67</t>
+          <t>-64,02; 37,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,97; -5,81</t>
+          <t>-43,02; 25,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 27,03</t>
+          <t>-70,38; -14,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,12; -5,42</t>
+          <t>-42,82; -3,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,48; 11,25</t>
+          <t>-60,39; 3,77</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,76</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-9,47</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>6,98</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-4,39</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-9,23</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-7,0</t>
+          <t>-6,53</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 20,36</t>
+          <t>-13,62; 8,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 7,11</t>
+          <t>-19,91; 2,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 8,5</t>
+          <t>-6,83; 18,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 2,7</t>
+          <t>-15,44; 9,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 10,18</t>
+          <t>-6,62; 10,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 1,13</t>
+          <t>-14,74; 2,08</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-12,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-41,18%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>33,01%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-20,76%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-12,0%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-40,15%</t>
+          <t>-15,79%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-31,48%</t>
+          <t>-29,36%</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 141,58</t>
+          <t>-49,37; 51,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-63,07; 48,87</t>
+          <t>-72,07; 19,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 49,58</t>
+          <t>-27,82; 127,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-70,8; 12,66</t>
+          <t>-58,05; 69,51</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 60,07</t>
+          <t>-25,72; 56,5</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 6,53</t>
+          <t>-56,47; 12,74</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-3,72</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-12,12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>2,29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-12,28</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-12,17</t>
+          <t>-11,41</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-12,14</t>
+          <t>-11,73</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,39</t>
+          <t>-8,17; -0,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -8,82</t>
+          <t>-16,34; -6,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 0,63</t>
+          <t>-1,62; 6,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -7,4</t>
+          <t>-15,51; -7,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,22</t>
+          <t>-3,39; 2,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -8,75</t>
+          <t>-14,88; -8,91</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-11,36%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-37,05%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-43,12%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-11,36%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-37,19%</t>
+          <t>-40,06%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-39,61%</t>
+          <t>-38,27%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 23,88</t>
+          <t>-23,22; -0,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,62; -32,0</t>
+          <t>-46,88; -21,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 2,15</t>
+          <t>-5,31; 25,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,97; -23,39</t>
+          <t>-51,06; -28,38</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 7,59</t>
+          <t>-10,6; 7,83</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,65; -29,66</t>
+          <t>-46,31; -29,48</t>
         </is>
       </c>
     </row>
